--- a/__EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/__EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9850,9 +9850,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C440607C-E549-4BEF-B157-82CD94A08CAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E7086F0-770B-4323-8BF9-02EC28EAB4FC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE194F6E-4C52-42E6-A1F0-3D2320B985AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{958A80CB-35A6-4507-9FC9-D9DC95A13CE9}"/>
 </file>